--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487941_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487941_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1091</v>
+        <v>6.6113</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9292</v>
+        <v>6.2348</v>
       </c>
       <c r="F2" t="n">
-        <v>0.18</v>
+        <v>0.3765</v>
       </c>
       <c r="G2" t="n">
         <v>5.6954</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9738</v>
+        <v>-0.4717</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4881</v>
+        <v>-0.1825</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4857</v>
+        <v>-0.2891</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0542</v>
+        <v>4.3623</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7357</v>
+        <v>3.2946</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3185</v>
+        <v>1.0677</v>
       </c>
       <c r="G3" t="n">
-        <v>3.953</v>
+        <v>2.1517</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1348</v>
+        <v>1.9356</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8181</v>
+        <v>0.2162</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3087</v>
+        <v>3.3143</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7737000000000001</v>
+        <v>2.5833</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5351</v>
+        <v>0.731</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6442</v>
+        <v>-1.1625</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3612</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2831</v>
+        <v>-0.5148</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0197</v>
+        <v>-0.858</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4885</v>
+        <v>-0.2356</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5082</v>
+        <v>-0.6224</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2666</v>
+        <v>1.0864</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0704</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1962</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7968</v>
+        <v>4.204</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7853</v>
+        <v>1.717</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0115</v>
+        <v>2.487</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1517</v>
+        <v>3.953</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9356</v>
+        <v>1.1348</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2162</v>
+        <v>2.8181</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3143</v>
+        <v>3.3087</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5833</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.731</v>
+        <v>2.5351</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1625</v>
+        <v>0.6442</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.3612</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5148</v>
+        <v>0.2831</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4236</v>
+        <v>-0.8699</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.745</v>
+        <v>-0.5302</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6786</v>
+        <v>-0.3397</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0864</v>
+        <v>-0.2666</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2071</v>
+        <v>-0.0704</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1207</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2405</v>
+        <v>3.7041</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3603</v>
+        <v>3.7678</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1198</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>1.2423</v>
@@ -844,13 +844,13 @@
         <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7444</v>
+        <v>-0.2808</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.745</v>
+        <v>-0.3375</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0567</v>
       </c>
       <c r="V5" t="n">
         <v>1.1568</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.824</v>
+        <v>1.3604</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0019</v>
+        <v>0.5944</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.766</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9686</v>
@@ -922,13 +922,13 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3098</v>
+        <v>0.8462</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5068</v>
+        <v>0.0993</v>
       </c>
       <c r="U6" t="n">
-        <v>0.803</v>
+        <v>0.7469</v>
       </c>
       <c r="V6" t="n">
         <v>1.0864</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4522</v>
+        <v>0.2877</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5379</v>
+        <v>-3.0286</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9902</v>
+        <v>3.3163</v>
       </c>
       <c r="G7" t="n">
         <v>0.8234</v>
@@ -1000,13 +1000,13 @@
         <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1007</v>
+        <v>-0.2653</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8625</v>
+        <v>-0.3532</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7618</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8651</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5701</v>
+        <v>-1.4715</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7992</v>
+        <v>-0.3917</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7709</v>
+        <v>-1.0797</v>
       </c>
       <c r="G8" t="n">
         <v>-2.9901</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3859</v>
+        <v>-0.2873</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6753</v>
+        <v>-0.2679</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2895</v>
+        <v>-0.0194</v>
       </c>
       <c r="V8" t="n">
         <v>0.8148</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0874</v>
+        <v>-1.6871</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2599</v>
+        <v>-1.0562</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8275</v>
+        <v>-0.6309</v>
       </c>
       <c r="G9" t="n">
         <v>0.3332</v>
@@ -1156,13 +1156,13 @@
         <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.181</v>
+        <v>0.2193</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1286</v>
+        <v>0.3323</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3095</v>
+        <v>-0.113</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6539</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2105</v>
+        <v>-3.1263</v>
       </c>
       <c r="E10" t="n">
         <v>-3.5277</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3171</v>
+        <v>0.4014</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8278</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9863</v>
+        <v>-0.9021</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4992</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4871</v>
+        <v>-0.4029</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9833</v>
+        <v>-4.6193</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.349</v>
+        <v>-4.2658</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6343</v>
+        <v>-0.3535</v>
       </c>
       <c r="G11" t="n">
         <v>-2.434</v>
@@ -1312,13 +1312,13 @@
         <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5874</v>
+        <v>-0.0486</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4244</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.837</v>
+        <v>-0.5562</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7403</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.625500000000002</v>
+        <v>9.625600000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>3.338699999999999</v>
+        <v>3.3386</v>
       </c>
       <c r="F12" t="n">
-        <v>6.286900000000001</v>
+        <v>6.2871</v>
       </c>
       <c r="G12" t="n">
         <v>5.978500000000001</v>
@@ -1366,7 +1366,7 @@
         <v>12.0817</v>
       </c>
       <c r="K12" t="n">
-        <v>8.263500000000001</v>
+        <v>8.263499999999999</v>
       </c>
       <c r="L12" t="n">
         <v>3.8182</v>
@@ -1375,7 +1375,7 @@
         <v>-6.1031</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.5665</v>
+        <v>-5.566500000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-0.5365000000000001</v>
@@ -1393,7 +1393,7 @@
         <v>-2.9182</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4668</v>
+        <v>-1.4669</v>
       </c>
       <c r="U12" t="n">
         <v>-1.4512</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5482</v>
+        <v>4.4789</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6441</v>
+        <v>2.4217</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9041</v>
+        <v>2.0571</v>
       </c>
       <c r="G13" t="n">
         <v>2.8258</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>4.337</v>
+        <v>2.2676</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0632</v>
+        <v>0.8408</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2737</v>
+        <v>1.4268</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0109</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0006</v>
+        <v>1.3513</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5053</v>
+        <v>2.4221</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5047</v>
+        <v>-1.0708</v>
       </c>
       <c r="G14" t="n">
         <v>0.032</v>
@@ -1546,13 +1546,13 @@
         <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2549</v>
+        <v>0.6056</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9029</v>
+        <v>0.014</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1578</v>
+        <v>0.5917</v>
       </c>
       <c r="V14" t="n">
         <v>-0.674</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1382</v>
+        <v>0.1371</v>
       </c>
       <c r="E16" t="n">
-        <v>1.24</v>
+        <v>0.2194</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3782</v>
+        <v>-0.0824</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3502</v>
+        <v>2.2469</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0236</v>
+        <v>1.1354</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6734</v>
+        <v>1.1115</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6122</v>
+        <v>3.2229</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2914</v>
+        <v>2.536</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6791</v>
+        <v>0.6869</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.262</v>
+        <v>-0.9761</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2677</v>
+        <v>-1.4007</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0057</v>
+        <v>0.4246</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7929</v>
+        <v>-1.784</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5294</v>
+        <v>-0.3258</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6278</v>
+        <v>-0.0302</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0984</v>
+        <v>-0.2956</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4937</v>
+        <v>0.0047</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1176</v>
+        <v>-0.3975</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6113</v>
+        <v>0.4022</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2469</v>
+        <v>-0.9755</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1354</v>
+        <v>1.2495</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1115</v>
+        <v>-2.2251</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2229</v>
+        <v>0.5831</v>
       </c>
       <c r="K17" t="n">
-        <v>2.536</v>
+        <v>1.8973</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6869</v>
+        <v>-1.3142</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9761</v>
+        <v>-1.5586</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4007</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4246</v>
+        <v>-0.9109</v>
       </c>
       <c r="P17" t="n">
         <v>-1.784</v>
@@ -1780,28 +1780,28 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9566</v>
+        <v>0.0835</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.132</v>
+        <v>-0.2806</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8245</v>
+        <v>0.3641</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.2734</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7795</v>
+        <v>-0.2858</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6012</v>
+        <v>1.0363</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1783</v>
+        <v>-1.322</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9755</v>
+        <v>0.3502</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2495</v>
+        <v>1.0236</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2251</v>
+        <v>-0.6734</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5831</v>
+        <v>0.6122</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8973</v>
+        <v>1.2914</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3142</v>
+        <v>-0.6791</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5586</v>
+        <v>-0.262</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.2677</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9109</v>
+        <v>0.0057</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7007</v>
+        <v>0.3818</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4844</v>
+        <v>0.424</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2164</v>
+        <v>-0.0422</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6808</v>
+        <v>-1.8107</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2734</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4074</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8912</v>
+        <v>-1.2706</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1046</v>
+        <v>-0.5121</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7866</v>
+        <v>-0.7585</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1926</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3014</v>
+        <v>-0.078</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5543</v>
+        <v>0.1469</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7907</v>
+        <v>-2.4747</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9293</v>
+        <v>-0.7255</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8615</v>
+        <v>-1.7491</v>
       </c>
       <c r="G20" t="n">
         <v>0.1888</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2481</v>
+        <v>0.0679</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1872</v>
+        <v>0.0165</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0609</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7403</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7931</v>
+        <v>-3.1845</v>
       </c>
       <c r="E21" t="n">
         <v>-3.9336</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1405</v>
+        <v>0.7491</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9188</v>
@@ -2092,13 +2092,13 @@
         <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0485</v>
+        <v>0.6571</v>
       </c>
       <c r="T21" t="n">
         <v>0.2058</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1573</v>
+        <v>0.4513</v>
       </c>
       <c r="V21" t="n">
         <v>0.8701</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2607</v>
+        <v>-3.8349</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2261</v>
+        <v>-4.4997</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0346</v>
+        <v>0.6647</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0396</v>
+        <v>-3.4036</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2067</v>
+        <v>-2.4183</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8329</v>
+        <v>-0.9853</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9145</v>
+        <v>-2.045</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2756</v>
+        <v>-1.2972</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.639</v>
+        <v>-0.7478</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1251</v>
+        <v>-1.3586</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9312</v>
+        <v>-1.1212</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1939</v>
+        <v>-0.2374</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9822</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>0.228</v>
+        <v>0.2249</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1286</v>
+        <v>-0.0145</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0994</v>
+        <v>0.2393</v>
       </c>
       <c r="V22" t="n">
         <v>0.5331</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9352</v>
+        <v>-4.0968</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9071</v>
+        <v>-3.2261</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0281</v>
+        <v>-0.8707</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4036</v>
+        <v>-3.0396</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4183</v>
+        <v>-1.2067</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9853</v>
+        <v>-1.8329</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.045</v>
+        <v>-0.9145</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2972</v>
+        <v>-0.2756</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7478</v>
+        <v>-0.639</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3586</v>
+        <v>-2.1251</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1212</v>
+        <v>-0.9312</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2374</v>
+        <v>-1.1939</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8754999999999999</v>
+        <v>0.3919</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.422</v>
+        <v>0.1286</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4535</v>
+        <v>0.2633</v>
       </c>
       <c r="V23" t="n">
         <v>0.5331</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.625499999999999</v>
+        <v>-8.267299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.286900000000001</v>
+        <v>-6.287000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3387</v>
+        <v>-1.9804</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.978400000000001</v>
+        <v>-5.9784</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.6969</v>
+        <v>-2.696899999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-3.2817</v>
@@ -2326,13 +2326,13 @@
         <v>11.8934</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9183</v>
+        <v>4.2765</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4512</v>
+        <v>1.4513</v>
       </c>
       <c r="U24" t="n">
-        <v>1.467</v>
+        <v>2.8252</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6187999999999995</v>
